--- a/wk3/python_Excel.xlsx
+++ b/wk3/python_Excel.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11011"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop W11\working_folder\Personales\Upright\Data_Science\Instructor_material\wk3\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/jatin/Desktop/Learnings/Upright/Student_Repo/wk3/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BED6573B-4012-47AB-BB4C-58CBA0164927}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63F15BF1-F7AF-014E-81B2-5EC1518F58EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="19090" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{8516C1E8-9EA0-482A-91C9-2CE1A2DB7C28}"/>
+    <workbookView xWindow="9980" yWindow="660" windowWidth="19420" windowHeight="17000" xr2:uid="{8516C1E8-9EA0-482A-91C9-2CE1A2DB7C28}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -184,7 +184,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1" indent="1" readingOrder="1"/>
     </xf>
   </cellXfs>
@@ -1278,16 +1278,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5F42948C-A579-4CF2-B45D-6BC7113BD4CF}">
   <dimension ref="A1:C7"/>
-  <sheetFormatPr defaultRowHeight="14.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="30.109375" customWidth="1"/>
-    <col min="2" max="2" width="17.21875" customWidth="1"/>
-    <col min="3" max="3" width="16.88671875" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" customWidth="1"/>
-    <col min="6" max="6" width="13.21875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="30.1640625" customWidth="1"/>
+    <col min="2" max="2" width="17.1640625" customWidth="1"/>
+    <col min="3" max="3" width="16.83203125" customWidth="1"/>
+    <col min="4" max="4" width="13.1640625" customWidth="1"/>
+    <col min="6" max="6" width="13.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="41.4">
+    <row r="1" spans="1:3" ht="30">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1298,7 +1298,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:3" ht="26.4">
+    <row r="2" spans="1:3" ht="28">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -1307,7 +1307,7 @@
       </c>
       <c r="C2" s="1"/>
     </row>
-    <row r="3" spans="1:3" ht="26.4">
+    <row r="3" spans="1:3" ht="28">
       <c r="A3" s="5" t="s">
         <v>4</v>
       </c>
@@ -1316,7 +1316,7 @@
       </c>
       <c r="C3" s="1"/>
     </row>
-    <row r="4" spans="1:3" ht="26.4">
+    <row r="4" spans="1:3" ht="28">
       <c r="A4" s="5" t="s">
         <v>2</v>
       </c>
@@ -1325,7 +1325,7 @@
       </c>
       <c r="C4" s="1"/>
     </row>
-    <row r="7" spans="1:3" ht="171.6">
+    <row r="7" spans="1:3" ht="140">
       <c r="A7" s="7" t="s">
         <v>9</v>
       </c>
